--- a/docs/generated/Заявки.xlsx
+++ b/docs/generated/Заявки.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -606,36 +606,40 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00086</t>
+          <t>DIM-2026-00090</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46284.77266203704</v>
+        <v>46284.85246527778</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -650,7 +654,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>46285.77266203704</v>
+        <v>46287.85246527778</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>4</v>
@@ -675,47 +679,43 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Свободная заявка с формы контактов</t>
+          <t>Заявка на подключение партнёра</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00087</t>
+          <t>DIM-2026-00089</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46284.77266203704</v>
+        <v>46284.8524537037</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>ТестСтрой SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>46287.77266203704</v>
+        <v>46285.8524537037</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>4</v>
@@ -755,18 +755,18 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Заявка на подключение партнёра</t>
+          <t>Свободная заявка с формы контактов</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00085</t>
+          <t>DIM-2026-00088</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46284.77265046296</v>
+        <v>46284.85244212963</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -850,11 +850,11 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00084</t>
+          <t>DIM-2026-00086</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46284.7725462963</v>
+        <v>46284.77266203704</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -863,64 +863,44 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>GROVE GMK 5100</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.77266203704</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -932,21 +912,25 @@
         </is>
       </c>
       <c r="T5" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00083</t>
+          <t>DIM-2026-00087</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46284.7725</v>
+        <v>46284.77266203704</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -955,22 +939,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -978,13 +962,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -992,123 +972,119 @@
       <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> КС-3577</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46287.77266203704</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T6" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00082</t>
+          <t>DIM-2026-00085</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46284.7725</v>
+        <v>46284.77265046296</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> КС-3577</t>
+          <t>GROVE GMK 5100</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T7" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>0</v>
@@ -1118,11 +1094,11 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00081</t>
+          <t>DIM-2026-00084</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46284.76486111111</v>
+        <v>46284.7725462963</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1136,15 +1112,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -1156,7 +1136,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>3</v>
@@ -1177,7 +1157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1196,7 +1176,7 @@
         </is>
       </c>
       <c r="T8" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>0</v>
@@ -1206,81 +1186,85 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00080</t>
+          <t>DIM-2026-00083</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46284.76190972222</v>
+        <v>46284.7725</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T9" s="4" t="n">
-        <v>57870</v>
+        <v>10260</v>
       </c>
       <c r="U9" s="4" t="n">
         <v>0</v>
@@ -1290,11 +1274,11 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00079</t>
+          <t>DIM-2026-00082</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46284.75966435186</v>
+        <v>46284.7725</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1303,22 +1287,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1326,9 +1310,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -1336,45 +1324,49 @@
       <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N10" s="3" t="n">
-        <v>46287.75966435186</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00077</t>
+          <t>DIM-2026-00081</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46284.75965277778</v>
+        <v>46284.76486111111</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1414,9 +1406,13 @@
         <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="n">
         <v>46296.375</v>
       </c>
@@ -1425,7 +1421,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1435,16 +1431,16 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T11" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>0</v>
@@ -1454,11 +1450,11 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00078</t>
+          <t>DIM-2026-00080</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46284.75965277778</v>
+        <v>46284.76190972222</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1467,44 +1463,56 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="3" t="n">
-        <v>46285.75965277778</v>
+        <v>46296.375</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -1516,87 +1524,71 @@
         </is>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00076</t>
+          <t>DIM-2026-00079</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46284.75954861111</v>
+        <v>46284.75966435186</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.75966435186</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -1608,59 +1600,55 @@
         </is>
       </c>
       <c r="T13" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00075</t>
+          <t>DIM-2026-00078</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46284.75950231482</v>
+        <v>46284.75965277778</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1670,113 +1658,113 @@
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.75965277778</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T14" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00074</t>
+          <t>DIM-2026-00077</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46284.75950231482</v>
+        <v>46284.75965277778</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T15" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
@@ -1786,11 +1774,11 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00073</t>
+          <t>DIM-2026-00076</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46284.75013888889</v>
+        <v>46284.75954861111</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1804,15 +1792,19 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -1824,7 +1816,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>3</v>
@@ -1841,7 +1833,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1860,7 +1852,7 @@
         </is>
       </c>
       <c r="T16" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
@@ -1870,11 +1862,11 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00072</t>
+          <t>DIM-2026-00075</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46284.74950231481</v>
+        <v>46284.75950231482</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1883,22 +1875,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1906,9 +1898,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1918,73 +1914,81 @@
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="3" t="n">
-        <v>46287.74950231481</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00071</t>
+          <t>DIM-2026-00074</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46284.74949074074</v>
+        <v>46284.75950231482</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1994,43 +1998,43 @@
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="3" t="n">
-        <v>46285.74949074074</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00070</t>
+          <t>DIM-2026-00073</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46284.74947916667</v>
+        <v>46284.75013888889</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -2070,7 +2074,7 @@
         <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="3" t="n">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2091,16 +2095,16 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T19" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>0</v>
@@ -2110,73 +2114,61 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00069</t>
+          <t>DIM-2026-00072</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46284.74938657408</v>
+        <v>46284.74950231481</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.74950231481</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2188,59 +2180,55 @@
         </is>
       </c>
       <c r="T20" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00067</t>
+          <t>DIM-2026-00071</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46284.74935185185</v>
+        <v>46284.74949074074</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -2250,113 +2238,113 @@
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46285.74949074074</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T21" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00068</t>
+          <t>DIM-2026-00070</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46284.74935185185</v>
+        <v>46284.74947916667</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T22" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>0</v>
@@ -2366,11 +2354,11 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00066</t>
+          <t>DIM-2026-00069</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46284.66527777778</v>
+        <v>46284.74938657408</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -2384,15 +2372,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -2404,7 +2396,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>3</v>
@@ -2421,7 +2413,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2440,7 +2432,7 @@
         </is>
       </c>
       <c r="T23" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>0</v>
@@ -2450,11 +2442,11 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00065</t>
+          <t>DIM-2026-00068</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46284.664375</v>
+        <v>46284.74935185185</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -2463,22 +2455,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2486,9 +2478,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -2498,73 +2494,81 @@
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="3" t="n">
-        <v>46287.664375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00064</t>
+          <t>DIM-2026-00067</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46284.66436342592</v>
+        <v>46284.74935185185</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -2574,43 +2578,43 @@
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="3" t="n">
-        <v>46285.66436342592</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00063</t>
+          <t>DIM-2026-00066</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46284.66435185185</v>
+        <v>46284.66527777778</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
         <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="3" t="n">
@@ -2661,7 +2665,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2671,16 +2675,16 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T26" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>0</v>
@@ -2690,73 +2694,61 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00062</t>
+          <t>DIM-2026-00065</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46284.66431712963</v>
+        <v>46284.664375</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.664375</v>
       </c>
       <c r="O27" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2768,59 +2760,55 @@
         </is>
       </c>
       <c r="T27" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00061</t>
+          <t>DIM-2026-00064</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46284.66429398148</v>
+        <v>46284.66436342592</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -2830,113 +2818,113 @@
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.66436342592</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T28" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00060</t>
+          <t>DIM-2026-00063</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46284.66428240741</v>
+        <v>46284.66435185185</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T29" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U29" s="4" t="n">
         <v>0</v>
@@ -2946,61 +2934,73 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00059</t>
+          <t>DIM-2026-00062</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46284.63960648148</v>
+        <v>46284.66431712963</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="3" t="n">
-        <v>46287.63960648148</v>
+        <v>46296.375</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -3012,55 +3012,59 @@
         </is>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00058</t>
+          <t>DIM-2026-00061</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46284.63959490741</v>
+        <v>46284.66429398148</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -3070,113 +3074,113 @@
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="3" t="n">
-        <v>46285.63959490741</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00057</t>
+          <t>DIM-2026-00060</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46284.63959490741</v>
+        <v>46284.66428240741</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T32" s="4" t="n">
-        <v>62480</v>
+        <v>10260</v>
       </c>
       <c r="U32" s="4" t="n">
         <v>0</v>
@@ -3186,73 +3190,61 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00056</t>
+          <t>DIM-2026-00059</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46284.63946759259</v>
+        <v>46284.63960648148</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.63960648148</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -3264,59 +3256,55 @@
         </is>
       </c>
       <c r="T33" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00055</t>
+          <t>DIM-2026-00058</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46284.63944444444</v>
+        <v>46284.63959490741</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -3326,113 +3314,113 @@
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.63959490741</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T34" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00054</t>
+          <t>DIM-2026-00057</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46284.63943287037</v>
+        <v>46284.63959490741</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T35" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U35" s="4" t="n">
         <v>0</v>
@@ -3442,11 +3430,11 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00053</t>
+          <t>DIM-2026-00056</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46284.59835648148</v>
+        <v>46284.63946759259</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -3460,15 +3448,19 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -3480,7 +3472,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>3</v>
@@ -3497,7 +3489,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -3516,7 +3508,7 @@
         </is>
       </c>
       <c r="T36" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U36" s="4" t="n">
         <v>0</v>
@@ -3526,85 +3518,81 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00052</t>
+          <t>DIM-2026-00055</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46284.59787037037</v>
+        <v>46284.63944444444</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T37" s="4" t="n">
-        <v>61170</v>
+        <v>10260</v>
       </c>
       <c r="U37" s="4" t="n">
         <v>0</v>
@@ -3614,11 +3602,11 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00051</t>
+          <t>DIM-2026-00054</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46284.59783564815</v>
+        <v>46284.63943287037</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -3666,7 +3654,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>8</v>
@@ -3698,81 +3686,81 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00050</t>
+          <t>DIM-2026-00053</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46284.59783564815</v>
+        <v>46284.59835648148</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T39" s="4" t="n">
-        <v>10260</v>
+        <v>57870</v>
       </c>
       <c r="U39" s="4" t="n">
         <v>0</v>
@@ -3782,11 +3770,11 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00049</t>
+          <t>DIM-2026-00052</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46284.5900925926</v>
+        <v>46284.59787037037</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -3870,11 +3858,11 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00048</t>
+          <t>DIM-2026-00051</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46284.59005787037</v>
+        <v>46284.59783564815</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -3954,11 +3942,11 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00047</t>
+          <t>DIM-2026-00050</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46284.59005787037</v>
+        <v>46284.59783564815</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -4038,61 +4026,73 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00046</t>
+          <t>DIM-2026-00049</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46284.5899074074</v>
+        <v>46284.5900925926</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="3" t="n">
-        <v>46287.5899074074</v>
+        <v>46296.375</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -4104,55 +4104,59 @@
         </is>
       </c>
       <c r="T43" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00045</t>
+          <t>DIM-2026-00047</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46284.58989583333</v>
+        <v>46284.59005787037</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -4162,113 +4166,113 @@
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="3" t="n">
-        <v>46285.58989583333</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P44" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T44" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00044</t>
+          <t>DIM-2026-00048</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46284.58989583333</v>
+        <v>46284.59005787037</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T45" s="4" t="n">
-        <v>62480</v>
+        <v>10260</v>
       </c>
       <c r="U45" s="4" t="n">
         <v>0</v>
@@ -4278,69 +4282,61 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00043</t>
+          <t>DIM-2026-00046</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46284.58836805556</v>
+        <v>46284.5899074074</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.5899074074</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -4352,50 +4348,50 @@
         </is>
       </c>
       <c r="T46" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00042</t>
+          <t>DIM-2026-00045</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46284.58796296296</v>
+        <v>46284.58989583333</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>ТестСтрой SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -4410,7 +4406,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="3" t="n">
-        <v>46287.58796296296</v>
+        <v>46285.58989583333</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>4</v>
@@ -4435,18 +4431,18 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Заявка на подключение партнёра</t>
+          <t>Свободная заявка с формы контактов</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00041</t>
+          <t>DIM-2026-00044</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46284.58795138889</v>
+        <v>46284.58989583333</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -4455,74 +4451,82 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="3" t="n">
-        <v>46285.58795138889</v>
+        <v>46296.375</v>
       </c>
       <c r="O48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T48" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00040</t>
+          <t>DIM-2026-00043</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46284.58793981482</v>
+        <v>46284.58836805556</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -4562,7 +4566,7 @@
         <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="3" t="n">
@@ -4573,7 +4577,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -4583,16 +4587,16 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T49" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U49" s="4" t="n">
         <v>0</v>
@@ -4602,73 +4606,61 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00039</t>
+          <t>DIM-2026-00042</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46284.58790509259</v>
+        <v>46284.58796296296</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.58796296296</v>
       </c>
       <c r="O50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -4680,59 +4672,55 @@
         </is>
       </c>
       <c r="T50" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00038</t>
+          <t>DIM-2026-00041</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46284.58788194445</v>
+        <v>46284.58795138889</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -4742,113 +4730,113 @@
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.58795138889</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T51" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00037</t>
+          <t>DIM-2026-00040</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46284.58787037037</v>
+        <v>46284.58793981482</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T52" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U52" s="4" t="n">
         <v>0</v>
@@ -4858,11 +4846,11 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00036</t>
+          <t>DIM-2026-00039</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46284.58694444445</v>
+        <v>46284.58790509259</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
@@ -4876,15 +4864,19 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -4896,7 +4888,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>3</v>
@@ -4913,7 +4905,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -4932,7 +4924,7 @@
         </is>
       </c>
       <c r="T53" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U53" s="4" t="n">
         <v>0</v>
@@ -4942,85 +4934,81 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00035</t>
+          <t>DIM-2026-00038</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46284.58646990741</v>
+        <v>46284.58788194445</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T54" s="4" t="n">
-        <v>61170</v>
+        <v>10260</v>
       </c>
       <c r="U54" s="4" t="n">
         <v>0</v>
@@ -5030,11 +5018,11 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00034</t>
+          <t>DIM-2026-00037</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46284.58644675926</v>
+        <v>46284.58787037037</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -5082,7 +5070,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O55" s="2" t="n">
         <v>8</v>
@@ -5114,81 +5102,81 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00033</t>
+          <t>DIM-2026-00036</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46284.58643518519</v>
+        <v>46284.58694444445</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T56" s="4" t="n">
-        <v>10260</v>
+        <v>57870</v>
       </c>
       <c r="U56" s="4" t="n">
         <v>0</v>
@@ -5198,11 +5186,11 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00032</t>
+          <t>DIM-2026-00035</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>46284.58615740741</v>
+        <v>46284.58646990741</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -5286,11 +5274,11 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00031</t>
+          <t>DIM-2026-00034</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46284.58614583333</v>
+        <v>46284.58644675926</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
@@ -5360,7 +5348,7 @@
         </is>
       </c>
       <c r="T58" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U58" s="4" t="n">
         <v>0</v>
@@ -5370,11 +5358,11 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00030</t>
+          <t>DIM-2026-00033</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>46284.58613425926</v>
+        <v>46284.58643518519</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -5444,7 +5432,7 @@
         </is>
       </c>
       <c r="T59" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U59" s="4" t="n">
         <v>0</v>
@@ -5454,61 +5442,73 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00029</t>
+          <t>DIM-2026-00032</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46284.585625</v>
+        <v>46284.58615740741</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="3" t="n">
-        <v>46287.585625</v>
+        <v>46296.375</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -5520,55 +5520,59 @@
         </is>
       </c>
       <c r="T60" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00028</t>
+          <t>DIM-2026-00031</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>46284.58561342592</v>
+        <v>46284.58614583333</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -5578,21 +5582,25 @@
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="3" t="n">
-        <v>46285.58561342592</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P61" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T61" s="4" t="n">
@@ -5601,90 +5609,86 @@
       <c r="U61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00027</t>
+          <t>DIM-2026-00030</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46284.58560185185</v>
+        <v>46284.58613425926</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T62" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U62" s="4" t="n">
         <v>0</v>
@@ -5694,11 +5698,11 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00026</t>
+          <t>DIM-2026-00029</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46284.58523148148</v>
+        <v>46284.585625</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
@@ -5742,7 +5746,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="3" t="n">
-        <v>46287.58523148148</v>
+        <v>46287.585625</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>4</v>
@@ -5774,11 +5778,11 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00024</t>
+          <t>DIM-2026-00028</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46284.58521990741</v>
+        <v>46284.58561342592</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
@@ -5787,82 +5791,74 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58561342592</v>
       </c>
       <c r="O64" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T64" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00025</t>
+          <t>DIM-2026-00027</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46284.58521990741</v>
+        <v>46284.58560185185</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -5871,74 +5867,82 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>46285.58521990741</v>
+        <v>46296.375</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P65" s="2" t="inlineStr"/>
-      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T65" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00023</t>
+          <t>DIM-2026-00026</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46284.58506944445</v>
+        <v>46284.58523148148</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
@@ -5982,7 +5986,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="3" t="n">
-        <v>46287.58506944445</v>
+        <v>46287.58523148148</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
@@ -6014,11 +6018,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00022</t>
+          <t>DIM-2026-00024</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>46284.58505787037</v>
+        <v>46284.58521990741</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
@@ -6027,74 +6031,82 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="3" t="n">
-        <v>46285.58505787037</v>
+        <v>46296.375</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P67" s="2" t="inlineStr"/>
-      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T67" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00021</t>
+          <t>DIM-2026-00025</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46284.5850462963</v>
+        <v>46284.58521990741</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
@@ -6103,82 +6115,74 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58521990741</v>
       </c>
       <c r="O68" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T68" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00020</t>
+          <t>DIM-2026-00023</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>46284.58466435185</v>
+        <v>46284.58506944445</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
@@ -6222,7 +6226,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="3" t="n">
-        <v>46287.58466435185</v>
+        <v>46287.58506944445</v>
       </c>
       <c r="O69" s="2" t="n">
         <v>4</v>
@@ -6254,11 +6258,11 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00019</t>
+          <t>DIM-2026-00022</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>46284.58466435185</v>
+        <v>46284.58505787037</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
@@ -6298,7 +6302,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="3" t="n">
-        <v>46285.58466435185</v>
+        <v>46285.58505787037</v>
       </c>
       <c r="O70" s="2" t="n">
         <v>4</v>
@@ -6330,11 +6334,11 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00018</t>
+          <t>DIM-2026-00021</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>46284.58465277778</v>
+        <v>46284.5850462963</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
@@ -6414,73 +6418,61 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00017</t>
+          <t>DIM-2026-00020</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46284.57537037037</v>
+        <v>46284.58466435185</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.58466435185</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6492,59 +6484,55 @@
         </is>
       </c>
       <c r="T72" s="4" t="n">
-        <v>17930</v>
+        <v>0</v>
       </c>
       <c r="U72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00016</t>
+          <t>DIM-2026-00019</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>46284.57534722222</v>
+        <v>46284.58466435185</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -6554,113 +6542,113 @@
       </c>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.58466435185</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
       <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T73" s="4" t="n">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="U73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00015</t>
+          <t>DIM-2026-00018</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>46284.57534722222</v>
+        <v>46284.58465277778</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T74" s="4" t="n">
-        <v>23600</v>
+        <v>62480</v>
       </c>
       <c r="U74" s="4" t="n">
         <v>0</v>
@@ -6670,11 +6658,11 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00014</t>
+          <t>DIM-2026-00017</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>46284.57185185186</v>
+        <v>46284.57537037037</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
@@ -6688,15 +6676,19 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -6708,7 +6700,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>3</v>
@@ -6725,7 +6717,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -6744,7 +6736,7 @@
         </is>
       </c>
       <c r="T75" s="4" t="n">
-        <v>57870</v>
+        <v>17930</v>
       </c>
       <c r="U75" s="4" t="n">
         <v>0</v>
@@ -6754,81 +6746,81 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00013</t>
+          <t>DIM-2026-00016</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>46284.57065972222</v>
+        <v>46284.57534722222</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T76" s="4" t="n">
-        <v>57870</v>
+        <v>23600</v>
       </c>
       <c r="U76" s="4" t="n">
         <v>0</v>
@@ -6838,85 +6830,81 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00012</t>
+          <t>DIM-2026-00015</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>46284.56907407408</v>
+        <v>46284.57534722222</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T77" s="4" t="n">
-        <v>17930</v>
+        <v>23600</v>
       </c>
       <c r="U77" s="4" t="n">
         <v>0</v>
@@ -6926,81 +6914,81 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00011</t>
+          <t>DIM-2026-00014</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>46284.5690625</v>
+        <v>46284.57185185186</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T78" s="4" t="n">
-        <v>23600</v>
+        <v>57870</v>
       </c>
       <c r="U78" s="4" t="n">
         <v>0</v>
@@ -7010,81 +6998,81 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00010</t>
+          <t>DIM-2026-00013</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>46284.56905092593</v>
+        <v>46284.57065972222</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T79" s="4" t="n">
-        <v>23600</v>
+        <v>57870</v>
       </c>
       <c r="U79" s="4" t="n">
         <v>0</v>
@@ -7094,11 +7082,11 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00001</t>
+          <t>DIM-2026-00012</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.56907407408</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
@@ -7112,15 +7100,19 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Ион Русу</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>+37369111222</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -7142,29 +7134,33 @@
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>46286.94390046296</v>
+        <v>46296.375</v>
       </c>
       <c r="O80" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, с. Стэучень</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T80" s="4" t="n">
-        <v>9900</v>
+        <v>17930</v>
       </c>
       <c r="U80" s="4" t="n">
         <v>0</v>
@@ -7174,11 +7170,11 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00009</t>
+          <t>DIM-2026-00011</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.5690625</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -7212,11 +7208,11 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -7226,7 +7222,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="3" t="n">
-        <v>46291.3334837963</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>8</v>
@@ -7248,21 +7244,21 @@
         </is>
       </c>
       <c r="T81" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U81" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00008</t>
+          <t>DIM-2026-00010</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.56905092593</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
@@ -7296,11 +7292,11 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -7310,7 +7306,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>46284.3334837963</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O82" s="2" t="n">
         <v>8</v>
@@ -7323,26 +7319,26 @@
       <c r="Q82" s="2" t="inlineStr"/>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T82" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U82" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00007</t>
+          <t>DIM-2026-00001</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
@@ -7350,58 +7346,54 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Русу</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369111222</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="3" t="n">
-        <v>46277.3334837963</v>
+        <v>46286.94390046296</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
+          <t>Chișinău, с. Стэучень</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -7412,21 +7404,21 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T83" s="4" t="n">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="U83" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00006</t>
+          <t>DIM-2026-00009</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
@@ -7434,83 +7426,83 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Анна Ковальчук</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>+37379333444</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>lift_height</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Трансформатор</t>
+          <t>Бетонирование перекрытия</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>42</v>
+        <v>2.5</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="3" t="n">
-        <v>46293.86056712963</v>
+        <v>46291.3334837963</v>
       </c>
       <c r="O84" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, промзона</t>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T84" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="5" t="inlineStr">
-        <is>
-          <t>Масса груза превышает 60 % возможностей парка — требуется инженерный расчёт; Работа вблизи ЛЭП</t>
-        </is>
-      </c>
+        <v>16720</v>
+      </c>
+      <c r="V84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00005</t>
+          <t>DIM-2026-00008</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
@@ -7518,54 +7510,58 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Ион Русу</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>+37369111222</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Септик</t>
+          <t>Бетонирование перекрытия</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="3" t="n">
-        <v>46264.56890046296</v>
+        <v>46284.3334837963</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, с. Стэучень</t>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -7576,21 +7572,21 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="T85" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U85" s="4" t="n">
-        <v>6200</v>
+        <v>16720</v>
       </c>
       <c r="V85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00004</t>
+          <t>DIM-2026-00007</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
@@ -7598,54 +7594,58 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Виктор Чеботарь</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>+37360777888</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>unload</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Плиты перекрытия</t>
+          <t>Бетонирование перекрытия</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
         <v>2.5</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="3" t="n">
-        <v>46285.6522337963</v>
+        <v>46277.3334837963</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Мунчешть 271</t>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -7656,21 +7656,21 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="T86" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U86" s="4" t="n">
-        <v>6800</v>
+        <v>16720</v>
       </c>
       <c r="V86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00003</t>
+          <t>DIM-2026-00006</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
@@ -7683,17 +7683,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Сергей Мунтян</t>
+          <t>Анна Ковальчук</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+37368555666</t>
+          <t>+37379333444</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
@@ -7704,53 +7704,57 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Металлоферма</t>
+          <t>Трансформатор</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.8</v>
+        <v>42</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>46290.94390046296</v>
+        <v>46293.86056712963</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Узинелор 5</t>
+          <t>Chișinău, промзона</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T87" s="4" t="n">
         <v>0</v>
       </c>
       <c r="U87" s="4" t="n">
-        <v>17600</v>
-      </c>
-      <c r="V87" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="V87" s="5" t="inlineStr">
+        <is>
+          <t>Масса груза превышает 60 % возможностей парка — требуется инженерный расчёт; Работа вблизи ЛЭП</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00002</t>
+          <t>DIM-2026-00005</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
@@ -7768,122 +7772,362 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Анна Ковальчук</t>
+          <t>Ион Русу</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+37379333444</t>
+          <t>+37369111222</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>install</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Кондиционер / чиллер</t>
+          <t>Септик</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>46288.9022337963</v>
+        <v>46264.56890046296</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, бул. Дачия 47</t>
+          <t>Chișinău, с. Стэучень</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="T88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00004</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Виктор Чеботарь</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>+37360777888</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>unload</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Плиты перекрытия</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="3" t="n">
+        <v>46285.6522337963</v>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Мунчешть 271</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="T89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00003</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Сергей Мунтян</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>+37368555666</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>lift_height</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Металлоферма</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="3" t="n">
+        <v>46290.94390046296</v>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Узинелор 5</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="T90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="4" t="n">
+        <v>17600</v>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00002</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Анна Ковальчук</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>+37379333444</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Кондиционер / чиллер</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="3" t="n">
+        <v>46288.9022337963</v>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, бул. Дачия 47</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
           <t>contacted</t>
         </is>
       </c>
-      <c r="S88" s="2" t="inlineStr">
+      <c r="S91" s="2" t="inlineStr">
         <is>
           <t>under_review</t>
         </is>
       </c>
-      <c r="T88" s="4" t="n">
+      <c r="T91" s="4" t="n">
         <v>11200</v>
       </c>
-      <c r="U88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="2" t="n"/>
-      <c r="K89" s="2" t="n"/>
-      <c r="L89" s="2" t="n"/>
-      <c r="M89" s="2" t="n"/>
-      <c r="N89" s="2" t="n"/>
-      <c r="O89" s="2" t="n"/>
-      <c r="P89" s="2" t="n"/>
-      <c r="Q89" s="2" t="n"/>
-      <c r="R89" s="2" t="n"/>
-      <c r="S89" s="2" t="n"/>
-      <c r="T89" s="2" t="n"/>
-      <c r="U89" s="2" t="n"/>
-      <c r="V89" s="2" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="U91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="2" t="n"/>
+      <c r="L92" s="2" t="n"/>
+      <c r="M92" s="2" t="n"/>
+      <c r="N92" s="2" t="n"/>
+      <c r="O92" s="2" t="n"/>
+      <c r="P92" s="2" t="n"/>
+      <c r="Q92" s="2" t="n"/>
+      <c r="R92" s="2" t="n"/>
+      <c r="S92" s="2" t="n"/>
+      <c r="T92" s="2" t="n"/>
+      <c r="U92" s="2" t="n"/>
+      <c r="V92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr"/>
-      <c r="C90" s="6" t="inlineStr"/>
-      <c r="D90" s="6" t="inlineStr"/>
-      <c r="E90" s="6" t="inlineStr"/>
-      <c r="F90" s="6" t="inlineStr"/>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr"/>
-      <c r="I90" s="6" t="inlineStr"/>
-      <c r="J90" s="6" t="inlineStr"/>
-      <c r="K90" s="6" t="inlineStr"/>
-      <c r="L90" s="6" t="inlineStr"/>
-      <c r="M90" s="6" t="inlineStr"/>
-      <c r="N90" s="6" t="inlineStr"/>
-      <c r="O90" s="6" t="inlineStr"/>
-      <c r="P90" s="6" t="inlineStr"/>
-      <c r="Q90" s="6" t="inlineStr"/>
-      <c r="R90" s="6" t="inlineStr"/>
-      <c r="S90" s="6" t="inlineStr"/>
-      <c r="T90" s="6">
-        <f>SUM(T2:T86)</f>
+      <c r="B93" s="6" t="inlineStr"/>
+      <c r="C93" s="6" t="inlineStr"/>
+      <c r="D93" s="6" t="inlineStr"/>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr"/>
+      <c r="J93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr"/>
+      <c r="M93" s="6" t="inlineStr"/>
+      <c r="N93" s="6" t="inlineStr"/>
+      <c r="O93" s="6" t="inlineStr"/>
+      <c r="P93" s="6" t="inlineStr"/>
+      <c r="Q93" s="6" t="inlineStr"/>
+      <c r="R93" s="6" t="inlineStr"/>
+      <c r="S93" s="6" t="inlineStr"/>
+      <c r="T93" s="6">
+        <f>SUM(T2:T89)</f>
         <v/>
       </c>
-      <c r="U90" s="6">
-        <f>SUM(U2:U86)</f>
+      <c r="U93" s="6">
+        <f>SUM(U2:U89)</f>
         <v/>
       </c>
-      <c r="V90" s="6" t="inlineStr"/>
+      <c r="V93" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>

--- a/docs/generated/Заявки.xlsx
+++ b/docs/generated/Заявки.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V93"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -606,11 +606,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00090</t>
+          <t>DIM-2026-00099</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46284.85246527778</v>
+        <v>46284.86627314815</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>46287.85246527778</v>
+        <v>46287.86627314815</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>4</v>
@@ -686,11 +686,11 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00089</t>
+          <t>DIM-2026-00098</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46284.8524537037</v>
+        <v>46284.86626157408</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>46285.8524537037</v>
+        <v>46285.86626157408</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>4</v>
@@ -762,11 +762,11 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00088</t>
+          <t>DIM-2026-00097</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46284.85244212963</v>
+        <v>46284.86626157408</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -850,11 +850,11 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00086</t>
+          <t>DIM-2026-00096</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46284.77266203704</v>
+        <v>46284.86613425926</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -863,44 +863,64 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N5" s="3" t="n">
-        <v>46285.77266203704</v>
+        <v>46296.375</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -912,25 +932,21 @@
         </is>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00087</t>
+          <t>DIM-2026-00095</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46284.77266203704</v>
+        <v>46284.86609953704</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -939,22 +955,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -962,9 +978,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -972,119 +992,123 @@
       <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N6" s="3" t="n">
-        <v>46287.77266203704</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00085</t>
+          <t>DIM-2026-00094</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46284.77265046296</v>
+        <v>46284.86608796296</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>GROVE GMK 5100</t>
+          <t xml:space="preserve"> КС-3577</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T7" s="4" t="n">
-        <v>62480</v>
+        <v>10260</v>
       </c>
       <c r="U7" s="4" t="n">
         <v>0</v>
@@ -1094,11 +1118,11 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00084</t>
+          <t>DIM-2026-00093</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46284.7725462963</v>
+        <v>46284.85287037037</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1186,11 +1210,11 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00083</t>
+          <t>DIM-2026-00092</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46284.7725</v>
+        <v>46284.85282407407</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1274,11 +1298,11 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00082</t>
+          <t>DIM-2026-00091</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46284.7725</v>
+        <v>46284.8528125</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1362,73 +1386,61 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00081</t>
+          <t>DIM-2026-00090</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46284.76486111111</v>
+        <v>46284.85246527778</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>GROVE GMK 5100</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.85246527778</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -1440,21 +1452,25 @@
         </is>
       </c>
       <c r="T11" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00080</t>
+          <t>DIM-2026-00089</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46284.76190972222</v>
+        <v>46284.8524537037</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1463,56 +1479,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.8524537037</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -1524,126 +1528,142 @@
         </is>
       </c>
       <c r="T12" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00079</t>
+          <t>DIM-2026-00088</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46284.75966435186</v>
+        <v>46284.85244212963</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ТестСтрой SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="n">
-        <v>46287.75966435186</v>
+        <v>46296.375</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00078</t>
+          <t>DIM-2026-00087</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46284.75965277778</v>
+        <v>46284.77266203704</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1658,7 +1678,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="3" t="n">
-        <v>46285.75965277778</v>
+        <v>46287.77266203704</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>4</v>
@@ -1683,18 +1703,18 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Свободная заявка с формы контактов</t>
+          <t>Заявка на подключение партнёра</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00077</t>
+          <t>DIM-2026-00086</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46284.75965277778</v>
+        <v>46284.77266203704</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1703,82 +1723,74 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.77266203704</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T15" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00076</t>
+          <t>DIM-2026-00085</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46284.75954861111</v>
+        <v>46284.77265046296</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1792,19 +1804,15 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -1816,15 +1824,19 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="n">
         <v>46296.375</v>
       </c>
@@ -1833,7 +1845,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1843,16 +1855,16 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T16" s="4" t="n">
-        <v>61170</v>
+        <v>62480</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
@@ -1862,81 +1874,89 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00075</t>
+          <t>DIM-2026-00084</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46284.75950231482</v>
+        <v>46284.7725462963</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T17" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>0</v>
@@ -1946,11 +1966,11 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00074</t>
+          <t>DIM-2026-00083</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46284.75950231482</v>
+        <v>46284.7725</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1996,9 +2016,13 @@
       <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N18" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>8</v>
@@ -2030,81 +2054,85 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00073</t>
+          <t>DIM-2026-00082</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46284.75013888889</v>
+        <v>46284.7725</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T19" s="4" t="n">
-        <v>57870</v>
+        <v>10260</v>
       </c>
       <c r="U19" s="4" t="n">
         <v>0</v>
@@ -2114,61 +2142,73 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00072</t>
+          <t>DIM-2026-00081</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46284.74950231481</v>
+        <v>46284.76486111111</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>ТестСтрой SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N20" s="3" t="n">
-        <v>46287.74950231481</v>
+        <v>46296.375</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2180,25 +2220,21 @@
         </is>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00071</t>
+          <t>DIM-2026-00080</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46284.74949074074</v>
+        <v>46284.76190972222</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -2207,44 +2243,56 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="3" t="n">
-        <v>46285.74949074074</v>
+        <v>46296.375</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2256,109 +2304,101 @@
         </is>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00070</t>
+          <t>DIM-2026-00079</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46284.74947916667</v>
+        <v>46284.75966435186</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.75966435186</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T22" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00069</t>
+          <t>DIM-2026-00077</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46284.74938657408</v>
+        <v>46284.75965277778</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -2372,19 +2412,15 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -2396,13 +2432,13 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="3" t="n">
@@ -2413,7 +2449,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2423,16 +2459,16 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T23" s="4" t="n">
-        <v>61170</v>
+        <v>62480</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>0</v>
@@ -2442,49 +2478,41 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00068</t>
+          <t>DIM-2026-00078</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46284.74935185185</v>
+        <v>46284.75965277778</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -2494,113 +2522,117 @@
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.75965277778</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T24" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00067</t>
+          <t>DIM-2026-00076</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46284.74935185185</v>
+        <v>46284.75954861111</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T25" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U25" s="4" t="n">
         <v>0</v>
@@ -2610,81 +2642,81 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00066</t>
+          <t>DIM-2026-00075</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46284.66527777778</v>
+        <v>46284.75950231482</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T26" s="4" t="n">
-        <v>57870</v>
+        <v>10260</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>0</v>
@@ -2694,11 +2726,11 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00065</t>
+          <t>DIM-2026-00074</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46284.664375</v>
+        <v>46284.75950231482</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -2707,22 +2739,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2730,9 +2762,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -2742,43 +2778,43 @@
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="3" t="n">
-        <v>46287.664375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P27" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00064</t>
+          <t>DIM-2026-00073</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46284.66436342592</v>
+        <v>46284.75013888889</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -2787,44 +2823,56 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="3" t="n">
-        <v>46285.66436342592</v>
+        <v>46296.375</v>
       </c>
       <c r="O28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2836,109 +2884,101 @@
         </is>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00063</t>
+          <t>DIM-2026-00072</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46284.66435185185</v>
+        <v>46284.74950231481</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.74950231481</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T29" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00062</t>
+          <t>DIM-2026-00071</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46284.66431712963</v>
+        <v>46284.74949074074</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -2947,60 +2987,44 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.74949074074</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -3012,91 +3036,95 @@
         </is>
       </c>
       <c r="T30" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00061</t>
+          <t>DIM-2026-00070</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46284.66429398148</v>
+        <v>46284.74947916667</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T31" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U31" s="4" t="n">
         <v>0</v>
@@ -3106,81 +3134,85 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00060</t>
+          <t>DIM-2026-00069</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46284.66428240741</v>
+        <v>46284.74938657408</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T32" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U32" s="4" t="n">
         <v>0</v>
@@ -3190,11 +3222,11 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00059</t>
+          <t>DIM-2026-00068</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46284.63960648148</v>
+        <v>46284.74935185185</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -3203,22 +3235,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3226,9 +3258,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -3238,73 +3274,81 @@
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="3" t="n">
-        <v>46287.63960648148</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00058</t>
+          <t>DIM-2026-00067</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46284.63959490741</v>
+        <v>46284.74935185185</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -3314,43 +3358,43 @@
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>46285.63959490741</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00057</t>
+          <t>DIM-2026-00066</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46284.63959490741</v>
+        <v>46284.66527777778</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -3390,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="3" t="n">
@@ -3401,7 +3445,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3411,16 +3455,16 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T35" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U35" s="4" t="n">
         <v>0</v>
@@ -3430,73 +3474,61 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00056</t>
+          <t>DIM-2026-00065</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46284.63946759259</v>
+        <v>46284.664375</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.664375</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -3508,59 +3540,55 @@
         </is>
       </c>
       <c r="T36" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00055</t>
+          <t>DIM-2026-00064</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46284.63944444444</v>
+        <v>46284.66436342592</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -3570,113 +3598,113 @@
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.66436342592</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T37" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00054</t>
+          <t>DIM-2026-00063</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46284.63943287037</v>
+        <v>46284.66435185185</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T38" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U38" s="4" t="n">
         <v>0</v>
@@ -3686,11 +3714,11 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00053</t>
+          <t>DIM-2026-00062</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46284.59835648148</v>
+        <v>46284.66431712963</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -3704,15 +3732,19 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -3724,7 +3756,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>3</v>
@@ -3741,7 +3773,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -3760,7 +3792,7 @@
         </is>
       </c>
       <c r="T39" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U39" s="4" t="n">
         <v>0</v>
@@ -3770,85 +3802,81 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00052</t>
+          <t>DIM-2026-00061</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46284.59787037037</v>
+        <v>46284.66429398148</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T40" s="4" t="n">
-        <v>61170</v>
+        <v>10260</v>
       </c>
       <c r="U40" s="4" t="n">
         <v>0</v>
@@ -3858,11 +3886,11 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00051</t>
+          <t>DIM-2026-00060</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46284.59783564815</v>
+        <v>46284.66428240741</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -3910,7 +3938,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O41" s="2" t="n">
         <v>8</v>
@@ -3942,11 +3970,11 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00050</t>
+          <t>DIM-2026-00059</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46284.59783564815</v>
+        <v>46284.63960648148</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -3955,22 +3983,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3978,13 +4006,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -3994,43 +4018,43 @@
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46287.63960648148</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T42" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00049</t>
+          <t>DIM-2026-00058</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46284.5900925926</v>
+        <v>46284.63959490741</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -4039,60 +4063,44 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.63959490741</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -4104,91 +4112,95 @@
         </is>
       </c>
       <c r="T43" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00047</t>
+          <t>DIM-2026-00057</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46284.59005787037</v>
+        <v>46284.63959490741</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T44" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U44" s="4" t="n">
         <v>0</v>
@@ -4198,81 +4210,85 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00048</t>
+          <t>DIM-2026-00056</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46284.59005787037</v>
+        <v>46284.63946759259</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T45" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U45" s="4" t="n">
         <v>0</v>
@@ -4282,11 +4298,11 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00046</t>
+          <t>DIM-2026-00055</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46284.5899074074</v>
+        <v>46284.63944444444</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
@@ -4295,22 +4311,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4318,9 +4334,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -4330,73 +4350,81 @@
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="3" t="n">
-        <v>46287.5899074074</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P46" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T46" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00045</t>
+          <t>DIM-2026-00054</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46284.58989583333</v>
+        <v>46284.63943287037</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -4406,43 +4434,43 @@
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="3" t="n">
-        <v>46285.58989583333</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T47" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00044</t>
+          <t>DIM-2026-00053</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46284.58989583333</v>
+        <v>46284.59835648148</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -4482,7 +4510,7 @@
         <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="3" t="n">
@@ -4493,7 +4521,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -4503,16 +4531,16 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T48" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U48" s="4" t="n">
         <v>0</v>
@@ -4522,11 +4550,11 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00043</t>
+          <t>DIM-2026-00052</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46284.58836805556</v>
+        <v>46284.59787037037</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -4540,15 +4568,19 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -4560,7 +4592,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>3</v>
@@ -4577,7 +4609,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -4596,7 +4628,7 @@
         </is>
       </c>
       <c r="T49" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U49" s="4" t="n">
         <v>0</v>
@@ -4606,11 +4638,11 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00042</t>
+          <t>DIM-2026-00051</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46284.58796296296</v>
+        <v>46284.59783564815</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -4619,22 +4651,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4642,9 +4674,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -4654,73 +4690,81 @@
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="3" t="n">
-        <v>46287.58796296296</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P50" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T50" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00041</t>
+          <t>DIM-2026-00050</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46284.58795138889</v>
+        <v>46284.59783564815</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -4730,43 +4774,43 @@
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="3" t="n">
-        <v>46285.58795138889</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P51" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T51" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00040</t>
+          <t>DIM-2026-00049</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46284.58793981482</v>
+        <v>46284.5900925926</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -4780,15 +4824,19 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -4800,13 +4848,13 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="3" t="n">
@@ -4817,7 +4865,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -4827,16 +4875,16 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T52" s="4" t="n">
-        <v>62480</v>
+        <v>61170</v>
       </c>
       <c r="U52" s="4" t="n">
         <v>0</v>
@@ -4846,85 +4894,81 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00039</t>
+          <t>DIM-2026-00048</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46284.58790509259</v>
+        <v>46284.59005787037</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T53" s="4" t="n">
-        <v>61170</v>
+        <v>10260</v>
       </c>
       <c r="U53" s="4" t="n">
         <v>0</v>
@@ -4934,11 +4978,11 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00038</t>
+          <t>DIM-2026-00047</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46284.58788194445</v>
+        <v>46284.59005787037</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
@@ -4986,7 +5030,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O54" s="2" t="n">
         <v>8</v>
@@ -5018,11 +5062,11 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00037</t>
+          <t>DIM-2026-00046</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46284.58787037037</v>
+        <v>46284.5899074074</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -5031,22 +5075,22 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -5054,13 +5098,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -5070,43 +5110,43 @@
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46287.5899074074</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
       <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T55" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00036</t>
+          <t>DIM-2026-00044</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46284.58694444445</v>
+        <v>46284.58989583333</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
@@ -5146,7 +5186,7 @@
         <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="3" t="n">
@@ -5157,7 +5197,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -5167,16 +5207,16 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T56" s="4" t="n">
-        <v>57870</v>
+        <v>62480</v>
       </c>
       <c r="U56" s="4" t="n">
         <v>0</v>
@@ -5186,11 +5226,11 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00035</t>
+          <t>DIM-2026-00045</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>46284.58646990741</v>
+        <v>46284.58989583333</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -5199,60 +5239,44 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58989583333</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
       <c r="R57" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -5264,91 +5288,95 @@
         </is>
       </c>
       <c r="T57" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00034</t>
+          <t>DIM-2026-00043</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46284.58644675926</v>
+        <v>46284.58836805556</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T58" s="4" t="n">
-        <v>10260</v>
+        <v>57870</v>
       </c>
       <c r="U58" s="4" t="n">
         <v>0</v>
@@ -5358,11 +5386,11 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00033</t>
+          <t>DIM-2026-00042</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>46284.58643518519</v>
+        <v>46284.58796296296</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -5371,22 +5399,22 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -5394,13 +5422,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -5410,43 +5434,43 @@
       </c>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46287.58796296296</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="2" t="inlineStr"/>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T59" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00032</t>
+          <t>DIM-2026-00041</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46284.58615740741</v>
+        <v>46284.58795138889</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
@@ -5455,60 +5479,44 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58795138889</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -5520,91 +5528,95 @@
         </is>
       </c>
       <c r="T60" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00031</t>
+          <t>DIM-2026-00040</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>46284.58614583333</v>
+        <v>46284.58793981482</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T61" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U61" s="4" t="n">
         <v>0</v>
@@ -5614,81 +5626,85 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00030</t>
+          <t>DIM-2026-00039</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46284.58613425926</v>
+        <v>46284.58790509259</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T62" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U62" s="4" t="n">
         <v>0</v>
@@ -5698,11 +5714,11 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00029</t>
+          <t>DIM-2026-00038</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46284.585625</v>
+        <v>46284.58788194445</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
@@ -5711,22 +5727,22 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5734,9 +5750,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -5746,73 +5766,81 @@
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="3" t="n">
-        <v>46287.585625</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P63" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T63" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00028</t>
+          <t>DIM-2026-00037</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46284.58561342592</v>
+        <v>46284.58787037037</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -5822,43 +5850,43 @@
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>46285.58561342592</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P64" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T64" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00027</t>
+          <t>DIM-2026-00036</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46284.58560185185</v>
+        <v>46284.58694444445</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -5898,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="3" t="n">
@@ -5909,7 +5937,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -5919,16 +5947,16 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T65" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U65" s="4" t="n">
         <v>0</v>
@@ -5938,61 +5966,73 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00026</t>
+          <t>DIM-2026-00035</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46284.58523148148</v>
+        <v>46284.58646990741</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="3" t="n">
-        <v>46287.58523148148</v>
+        <v>46296.375</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P66" s="2" t="inlineStr"/>
-      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6004,95 +6044,91 @@
         </is>
       </c>
       <c r="T66" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00024</t>
+          <t>DIM-2026-00034</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>46284.58521990741</v>
+        <v>46284.58644675926</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T67" s="4" t="n">
-        <v>62480</v>
+        <v>10260</v>
       </c>
       <c r="U67" s="4" t="n">
         <v>0</v>
@@ -6102,41 +6138,49 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00025</t>
+          <t>DIM-2026-00033</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46284.58521990741</v>
+        <v>46284.58643518519</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -6146,93 +6190,105 @@
       </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>46285.58521990741</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P68" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T68" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00023</t>
+          <t>DIM-2026-00032</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>46284.58506944445</v>
+        <v>46284.58615740741</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="3" t="n">
-        <v>46287.58506944445</v>
+        <v>46296.375</v>
       </c>
       <c r="O69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6244,55 +6300,59 @@
         </is>
       </c>
       <c r="T69" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00022</t>
+          <t>DIM-2026-00031</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>46284.58505787037</v>
+        <v>46284.58614583333</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -6302,21 +6362,25 @@
       </c>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="3" t="n">
-        <v>46285.58505787037</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P70" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q70" s="2" t="inlineStr"/>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T70" s="4" t="n">
@@ -6325,90 +6389,86 @@
       <c r="U70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00021</t>
+          <t>DIM-2026-00030</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>46284.5850462963</v>
+        <v>46284.58613425926</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T71" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U71" s="4" t="n">
         <v>0</v>
@@ -6418,11 +6478,11 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00020</t>
+          <t>DIM-2026-00029</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46284.58466435185</v>
+        <v>46284.585625</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -6466,7 +6526,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="3" t="n">
-        <v>46287.58466435185</v>
+        <v>46287.585625</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>4</v>
@@ -6498,11 +6558,11 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00019</t>
+          <t>DIM-2026-00028</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>46284.58466435185</v>
+        <v>46284.58561342592</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
@@ -6542,7 +6602,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="3" t="n">
-        <v>46285.58466435185</v>
+        <v>46285.58561342592</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>4</v>
@@ -6574,11 +6634,11 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00018</t>
+          <t>DIM-2026-00027</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>46284.58465277778</v>
+        <v>46284.58560185185</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -6658,73 +6718,61 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00017</t>
+          <t>DIM-2026-00026</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>46284.57537037037</v>
+        <v>46284.58523148148</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.58523148148</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr"/>
       <c r="R75" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6736,59 +6784,55 @@
         </is>
       </c>
       <c r="T75" s="4" t="n">
-        <v>17930</v>
+        <v>0</v>
       </c>
       <c r="U75" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00016</t>
+          <t>DIM-2026-00025</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>46284.57534722222</v>
+        <v>46284.58521990741</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
       <c r="J76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -6798,113 +6842,113 @@
       </c>
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.58521990741</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
       <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T76" s="4" t="n">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="U76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00015</t>
+          <t>DIM-2026-00024</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>46284.57534722222</v>
+        <v>46284.58521990741</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T77" s="4" t="n">
-        <v>23600</v>
+        <v>62480</v>
       </c>
       <c r="U77" s="4" t="n">
         <v>0</v>
@@ -6914,69 +6958,61 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00014</t>
+          <t>DIM-2026-00023</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>46284.57185185186</v>
+        <v>46284.58506944445</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.58506944445</v>
       </c>
       <c r="O78" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
       <c r="R78" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6988,21 +7024,25 @@
         </is>
       </c>
       <c r="T78" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00013</t>
+          <t>DIM-2026-00022</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>46284.57065972222</v>
+        <v>46284.58505787037</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
@@ -7011,56 +7051,44 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58505787037</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -7072,21 +7100,25 @@
         </is>
       </c>
       <c r="T79" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00012</t>
+          <t>DIM-2026-00021</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46284.56907407408</v>
+        <v>46284.5850462963</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
@@ -7100,19 +7132,15 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -7124,13 +7152,13 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="3" t="n">
@@ -7141,7 +7169,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -7151,16 +7179,16 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T80" s="4" t="n">
-        <v>17930</v>
+        <v>62480</v>
       </c>
       <c r="U80" s="4" t="n">
         <v>0</v>
@@ -7170,11 +7198,11 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00011</t>
+          <t>DIM-2026-00020</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>46284.5690625</v>
+        <v>46284.58466435185</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -7183,22 +7211,22 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -7206,13 +7234,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -7222,81 +7246,73 @@
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46287.58466435185</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
       <c r="Q81" s="2" t="inlineStr"/>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T81" s="4" t="n">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="U81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00010</t>
+          <t>DIM-2026-00019</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46284.56905092593</v>
+        <v>46284.58466435185</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -7306,43 +7322,43 @@
       </c>
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46285.58466435185</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
       <c r="Q82" s="2" t="inlineStr"/>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T82" s="4" t="n">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="U82" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00001</t>
+          <t>DIM-2026-00018</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.58465277778</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
@@ -7356,12 +7372,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Ион Русу</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>+37369111222</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
@@ -7376,30 +7392,34 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="3" t="n">
-        <v>46286.94390046296</v>
+        <v>46296.375</v>
       </c>
       <c r="O83" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, с. Стэучень</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
@@ -7408,7 +7428,7 @@
         </is>
       </c>
       <c r="T83" s="4" t="n">
-        <v>9900</v>
+        <v>62480</v>
       </c>
       <c r="U83" s="4" t="n">
         <v>0</v>
@@ -7418,95 +7438,99 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00009</t>
+          <t>DIM-2026-00017</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57537037037</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="3" t="n">
-        <v>46291.3334837963</v>
+        <v>46296.375</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T84" s="4" t="n">
-        <v>0</v>
+        <v>17930</v>
       </c>
       <c r="U84" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00008</t>
+          <t>DIM-2026-00016</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57534722222</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
@@ -7540,11 +7564,11 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -7554,7 +7578,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="3" t="n">
-        <v>46284.3334837963</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>8</v>
@@ -7567,30 +7591,30 @@
       <c r="Q85" s="2" t="inlineStr"/>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T85" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U85" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00007</t>
+          <t>DIM-2026-00015</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57534722222</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
@@ -7624,11 +7648,11 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -7638,7 +7662,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="3" t="n">
-        <v>46277.3334837963</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>8</v>
@@ -7651,30 +7675,30 @@
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T86" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U86" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00006</t>
+          <t>DIM-2026-00014</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57185185186</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
@@ -7688,47 +7712,51 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Анна Ковальчук</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+37379333444</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>lift_height</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Трансформатор</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>46293.86056712963</v>
+        <v>46296.375</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, промзона</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -7740,25 +7768,21 @@
         </is>
       </c>
       <c r="T87" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="5" t="inlineStr">
-        <is>
-          <t>Масса груза превышает 60 % возможностей парка — требуется инженерный расчёт; Работа вблизи ЛЭП</t>
-        </is>
-      </c>
+      <c r="V87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00005</t>
+          <t>DIM-2026-00013</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57065972222</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
@@ -7772,12 +7796,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Ион Русу</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+37369111222</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -7788,57 +7812,61 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Септик</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>46264.56890046296</v>
+        <v>46296.375</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, с. Стэучень</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T88" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U88" s="4" t="n">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00004</t>
+          <t>DIM-2026-00012</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.56907407408</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
@@ -7852,204 +7880,220 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Виктор Чеботарь</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>+37360777888</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>unload</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Плиты перекрытия</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>46285.6522337963</v>
+        <v>46296.375</v>
       </c>
       <c r="O89" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Мунчешть 271</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T89" s="4" t="n">
-        <v>0</v>
+        <v>17930</v>
       </c>
       <c r="U89" s="4" t="n">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="V89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00003</t>
+          <t>DIM-2026-00011</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.5690625</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Сергей Мунтян</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>+37368555666</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>lift_height</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Металлоферма</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="3" t="n">
-        <v>46290.94390046296</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O90" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Узинелор 5</t>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T90" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U90" s="4" t="n">
-        <v>17600</v>
+        <v>0</v>
       </c>
       <c r="V90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00002</t>
+          <t>DIM-2026-00010</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.56905092593</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Анна Ковальчук</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>+37379333444</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>install</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Кондиционер / чиллер</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="3" t="n">
-        <v>46288.9022337963</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, бул. Дачия 47</t>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
@@ -8064,70 +8108,806 @@
         </is>
       </c>
       <c r="T91" s="4" t="n">
+        <v>23600</v>
+      </c>
+      <c r="U91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Ион Русу</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>+37369111222</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="3" t="n">
+        <v>46286.94390046296</v>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, с. Стэучень</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="T92" s="4" t="n">
+        <v>9900</v>
+      </c>
+      <c r="U92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00009</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий Попа</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Бетонирование перекрытия</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="3" t="n">
+        <v>46291.3334837963</v>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>under_review</t>
+        </is>
+      </c>
+      <c r="T93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="4" t="n">
+        <v>16720</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00008</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий Попа</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Бетонирование перекрытия</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="3" t="n">
+        <v>46284.3334837963</v>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="T94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="4" t="n">
+        <v>16720</v>
+      </c>
+      <c r="V94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00007</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий Попа</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Бетонирование перекрытия</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="3" t="n">
+        <v>46277.3334837963</v>
+      </c>
+      <c r="O95" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="4" t="n">
+        <v>16720</v>
+      </c>
+      <c r="V95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00006</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Анна Ковальчук</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>+37379333444</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>lift_height</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Трансформатор</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="3" t="n">
+        <v>46293.86056712963</v>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, промзона</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="T96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="5" t="inlineStr">
+        <is>
+          <t>Масса груза превышает 60 % возможностей парка — требуется инженерный расчёт; Работа вблизи ЛЭП</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00005</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Ион Русу</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>+37369111222</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Септик</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="3" t="n">
+        <v>46264.56890046296</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, с. Стэучень</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="T97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="V97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00004</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Виктор Чеботарь</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>+37360777888</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>unload</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Плиты перекрытия</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="3" t="n">
+        <v>46285.6522337963</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Мунчешть 271</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="T98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="V98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00003</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Сергей Мунтян</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>+37368555666</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>lift_height</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Металлоферма</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="3" t="n">
+        <v>46290.94390046296</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Узинелор 5</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="T99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="4" t="n">
+        <v>17600</v>
+      </c>
+      <c r="V99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00002</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Анна Ковальчук</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>+37379333444</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Кондиционер / чиллер</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="3" t="n">
+        <v>46288.9022337963</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, бул. Дачия 47</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>under_review</t>
+        </is>
+      </c>
+      <c r="T100" s="4" t="n">
         <v>11200</v>
       </c>
-      <c r="U91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
-      <c r="J92" s="2" t="n"/>
-      <c r="K92" s="2" t="n"/>
-      <c r="L92" s="2" t="n"/>
-      <c r="M92" s="2" t="n"/>
-      <c r="N92" s="2" t="n"/>
-      <c r="O92" s="2" t="n"/>
-      <c r="P92" s="2" t="n"/>
-      <c r="Q92" s="2" t="n"/>
-      <c r="R92" s="2" t="n"/>
-      <c r="S92" s="2" t="n"/>
-      <c r="T92" s="2" t="n"/>
-      <c r="U92" s="2" t="n"/>
-      <c r="V92" s="2" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="U100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="2" t="n"/>
+      <c r="H101" s="2" t="n"/>
+      <c r="I101" s="2" t="n"/>
+      <c r="J101" s="2" t="n"/>
+      <c r="K101" s="2" t="n"/>
+      <c r="L101" s="2" t="n"/>
+      <c r="M101" s="2" t="n"/>
+      <c r="N101" s="2" t="n"/>
+      <c r="O101" s="2" t="n"/>
+      <c r="P101" s="2" t="n"/>
+      <c r="Q101" s="2" t="n"/>
+      <c r="R101" s="2" t="n"/>
+      <c r="S101" s="2" t="n"/>
+      <c r="T101" s="2" t="n"/>
+      <c r="U101" s="2" t="n"/>
+      <c r="V101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr"/>
-      <c r="C93" s="6" t="inlineStr"/>
-      <c r="D93" s="6" t="inlineStr"/>
-      <c r="E93" s="6" t="inlineStr"/>
-      <c r="F93" s="6" t="inlineStr"/>
-      <c r="G93" s="6" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr"/>
-      <c r="I93" s="6" t="inlineStr"/>
-      <c r="J93" s="6" t="inlineStr"/>
-      <c r="K93" s="6" t="inlineStr"/>
-      <c r="L93" s="6" t="inlineStr"/>
-      <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr"/>
-      <c r="O93" s="6" t="inlineStr"/>
-      <c r="P93" s="6" t="inlineStr"/>
-      <c r="Q93" s="6" t="inlineStr"/>
-      <c r="R93" s="6" t="inlineStr"/>
-      <c r="S93" s="6" t="inlineStr"/>
-      <c r="T93" s="6">
-        <f>SUM(T2:T89)</f>
+      <c r="B102" s="6" t="inlineStr"/>
+      <c r="C102" s="6" t="inlineStr"/>
+      <c r="D102" s="6" t="inlineStr"/>
+      <c r="E102" s="6" t="inlineStr"/>
+      <c r="F102" s="6" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr"/>
+      <c r="I102" s="6" t="inlineStr"/>
+      <c r="J102" s="6" t="inlineStr"/>
+      <c r="K102" s="6" t="inlineStr"/>
+      <c r="L102" s="6" t="inlineStr"/>
+      <c r="M102" s="6" t="inlineStr"/>
+      <c r="N102" s="6" t="inlineStr"/>
+      <c r="O102" s="6" t="inlineStr"/>
+      <c r="P102" s="6" t="inlineStr"/>
+      <c r="Q102" s="6" t="inlineStr"/>
+      <c r="R102" s="6" t="inlineStr"/>
+      <c r="S102" s="6" t="inlineStr"/>
+      <c r="T102" s="6">
+        <f>SUM(T2:T98)</f>
         <v/>
       </c>
-      <c r="U93" s="6">
-        <f>SUM(U2:U89)</f>
+      <c r="U102" s="6">
+        <f>SUM(U2:U98)</f>
         <v/>
       </c>
-      <c r="V93" s="6" t="inlineStr"/>
+      <c r="V102" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>

--- a/docs/generated/Заявки.xlsx
+++ b/docs/generated/Заявки.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:V111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -606,11 +606,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00099</t>
+          <t>DIM-2026-00108</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46284.86627314815</v>
+        <v>46284.96943287037</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>46287.86627314815</v>
+        <v>46287.96943287037</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>4</v>
@@ -686,11 +686,11 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00098</t>
+          <t>DIM-2026-00106</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>46284.86626157408</v>
+        <v>46284.96942129629</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -699,74 +699,86 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="n">
-        <v>46285.86626157408</v>
+        <v>46296.375</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00097</t>
+          <t>DIM-2026-00107</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>46284.86626157408</v>
+        <v>46284.96942129629</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -775,86 +787,74 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>GROVE GMK 5100</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.96942129629</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T4" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00096</t>
+          <t>DIM-2026-00105</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46284.86613425926</v>
+        <v>46284.96928240741</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -942,11 +942,11 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00095</t>
+          <t>DIM-2026-00103</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46284.86609953704</v>
+        <v>46284.96923611111</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>8</v>
@@ -1030,11 +1030,11 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00094</t>
+          <t>DIM-2026-00104</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46284.86608796296</v>
+        <v>46284.96923611111</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>8</v>
@@ -1118,11 +1118,11 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00093</t>
+          <t>DIM-2026-00102</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>46284.85287037037</v>
+        <v>46284.94591435185</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1210,11 +1210,11 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00092</t>
+          <t>DIM-2026-00101</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46284.85282407407</v>
+        <v>46284.94586805555</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1298,11 +1298,11 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00091</t>
+          <t>DIM-2026-00100</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46284.8528125</v>
+        <v>46284.94585648148</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00090</t>
+          <t>DIM-2026-00099</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46284.85246527778</v>
+        <v>46284.86627314815</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>46287.85246527778</v>
+        <v>46287.86627314815</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>4</v>
@@ -1466,11 +1466,11 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00089</t>
+          <t>DIM-2026-00097</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46284.8524537037</v>
+        <v>46284.86626157408</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1479,74 +1479,86 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N12" s="3" t="n">
-        <v>46285.8524537037</v>
+        <v>46296.375</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00088</t>
+          <t>DIM-2026-00098</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46284.85244212963</v>
+        <v>46284.86626157408</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1555,136 +1567,140 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>GROVE GMK 5100</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.86626157408</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T13" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00087</t>
+          <t>DIM-2026-00096</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>46284.77266203704</v>
+        <v>46284.86613425926</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="n">
-        <v>46287.77266203704</v>
+        <v>46296.375</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -1696,55 +1712,59 @@
         </is>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00086</t>
+          <t>DIM-2026-00095</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>46284.77266203704</v>
+        <v>46284.86609953704</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1752,119 +1772,123 @@
       <c r="L15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="n">
-        <v>46285.77266203704</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00085</t>
+          <t>DIM-2026-00094</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46284.77265046296</v>
+        <v>46284.86608796296</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>GROVE GMK 5100</t>
+          <t xml:space="preserve"> КС-3577</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T16" s="4" t="n">
-        <v>62480</v>
+        <v>10260</v>
       </c>
       <c r="U16" s="4" t="n">
         <v>0</v>
@@ -1874,11 +1898,11 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00084</t>
+          <t>DIM-2026-00093</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46284.7725462963</v>
+        <v>46284.85287037037</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1966,11 +1990,11 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00083</t>
+          <t>DIM-2026-00092</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46284.7725</v>
+        <v>46284.85282407407</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -2054,11 +2078,11 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00082</t>
+          <t>DIM-2026-00091</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46284.7725</v>
+        <v>46284.8528125</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -2142,73 +2166,61 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00081</t>
+          <t>DIM-2026-00090</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46284.76486111111</v>
+        <v>46284.85246527778</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>GROVE GMK 5100</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.85246527778</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2220,21 +2232,25 @@
         </is>
       </c>
       <c r="T20" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00080</t>
+          <t>DIM-2026-00089</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46284.76190972222</v>
+        <v>46284.8524537037</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -2243,56 +2259,44 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.8524537037</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2304,101 +2308,113 @@
         </is>
       </c>
       <c r="T21" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00079</t>
+          <t>DIM-2026-00088</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46284.75966435186</v>
+        <v>46284.85244212963</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>ТестСтрой SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N22" s="3" t="n">
-        <v>46287.75966435186</v>
+        <v>46296.375</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00077</t>
+          <t>DIM-2026-00086</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46284.75965277778</v>
+        <v>46284.77266203704</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -2407,107 +2423,103 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.77266203704</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T23" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00078</t>
+          <t>DIM-2026-00087</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46284.75965277778</v>
+        <v>46284.77266203704</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2522,7 +2534,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="3" t="n">
-        <v>46285.75965277778</v>
+        <v>46287.77266203704</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>4</v>
@@ -2547,18 +2559,18 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Свободная заявка с формы контактов</t>
+          <t>Заявка на подключение партнёра</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00076</t>
+          <t>DIM-2026-00085</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46284.75954861111</v>
+        <v>46284.77265046296</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -2572,19 +2584,15 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -2596,15 +2604,19 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N25" s="3" t="n">
         <v>46296.375</v>
       </c>
@@ -2613,7 +2625,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2623,16 +2635,16 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T25" s="4" t="n">
-        <v>61170</v>
+        <v>62480</v>
       </c>
       <c r="U25" s="4" t="n">
         <v>0</v>
@@ -2642,81 +2654,89 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00075</t>
+          <t>DIM-2026-00084</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46284.75950231482</v>
+        <v>46284.7725462963</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N26" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T26" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U26" s="4" t="n">
         <v>0</v>
@@ -2726,11 +2746,11 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00074</t>
+          <t>DIM-2026-00082</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>46284.75950231482</v>
+        <v>46284.7725</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -2776,7 +2796,11 @@
       <c r="L27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="n">
         <v>46301.33333333334</v>
       </c>
@@ -2810,81 +2834,85 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00073</t>
+          <t>DIM-2026-00083</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46284.75013888889</v>
+        <v>46284.7725</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> КС-3577</t>
+        </is>
+      </c>
       <c r="N28" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T28" s="4" t="n">
-        <v>57870</v>
+        <v>10260</v>
       </c>
       <c r="U28" s="4" t="n">
         <v>0</v>
@@ -2894,61 +2922,73 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00072</t>
+          <t>DIM-2026-00081</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46284.74950231481</v>
+        <v>46284.76486111111</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>ТестСтрой SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>GROVE GMK 5100</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="n">
-        <v>46287.74950231481</v>
+        <v>46296.375</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -2960,25 +3000,21 @@
         </is>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00071</t>
+          <t>DIM-2026-00080</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46284.74949074074</v>
+        <v>46284.76190972222</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -2987,44 +3023,56 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="3" t="n">
-        <v>46285.74949074074</v>
+        <v>46296.375</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -3036,109 +3084,101 @@
         </is>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00070</t>
+          <t>DIM-2026-00079</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46284.74947916667</v>
+        <v>46284.75966435186</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.75966435186</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T31" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00069</t>
+          <t>DIM-2026-00077</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46284.74938657408</v>
+        <v>46284.75965277778</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -3152,19 +3192,15 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -3176,13 +3212,13 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="3" t="n">
@@ -3193,7 +3229,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3203,16 +3239,16 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T32" s="4" t="n">
-        <v>61170</v>
+        <v>62480</v>
       </c>
       <c r="U32" s="4" t="n">
         <v>0</v>
@@ -3222,49 +3258,41 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00068</t>
+          <t>DIM-2026-00078</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46284.74935185185</v>
+        <v>46284.75965277778</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -3274,113 +3302,117 @@
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.75965277778</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T33" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00067</t>
+          <t>DIM-2026-00076</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46284.74935185185</v>
+        <v>46284.75954861111</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T34" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U34" s="4" t="n">
         <v>0</v>
@@ -3390,81 +3422,81 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00066</t>
+          <t>DIM-2026-00074</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46284.66527777778</v>
+        <v>46284.75950231482</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T35" s="4" t="n">
-        <v>57870</v>
+        <v>10260</v>
       </c>
       <c r="U35" s="4" t="n">
         <v>0</v>
@@ -3474,11 +3506,11 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00065</t>
+          <t>DIM-2026-00075</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46284.664375</v>
+        <v>46284.75950231482</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -3487,22 +3519,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3510,9 +3542,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -3522,43 +3558,43 @@
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="3" t="n">
-        <v>46287.664375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T36" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00064</t>
+          <t>DIM-2026-00073</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46284.66436342592</v>
+        <v>46284.75013888889</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -3567,44 +3603,56 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="3" t="n">
-        <v>46285.66436342592</v>
+        <v>46296.375</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -3616,109 +3664,101 @@
         </is>
       </c>
       <c r="T37" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00063</t>
+          <t>DIM-2026-00072</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46284.66435185185</v>
+        <v>46284.74950231481</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.74950231481</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T38" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00062</t>
+          <t>DIM-2026-00071</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46284.66431712963</v>
+        <v>46284.74949074074</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -3727,60 +3767,44 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.74949074074</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
       <c r="R39" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -3792,91 +3816,95 @@
         </is>
       </c>
       <c r="T39" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00061</t>
+          <t>DIM-2026-00070</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46284.66429398148</v>
+        <v>46284.74947916667</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T40" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U40" s="4" t="n">
         <v>0</v>
@@ -3886,81 +3914,85 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00060</t>
+          <t>DIM-2026-00069</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46284.66428240741</v>
+        <v>46284.74938657408</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T41" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U41" s="4" t="n">
         <v>0</v>
@@ -3970,11 +4002,11 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00059</t>
+          <t>DIM-2026-00067</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46284.63960648148</v>
+        <v>46284.74935185185</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -3983,22 +4015,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -4006,9 +4038,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -4018,73 +4054,81 @@
       </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="3" t="n">
-        <v>46287.63960648148</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P42" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T42" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00058</t>
+          <t>DIM-2026-00068</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46284.63959490741</v>
+        <v>46284.74935185185</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -4094,43 +4138,43 @@
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="3" t="n">
-        <v>46285.63959490741</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T43" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00057</t>
+          <t>DIM-2026-00066</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46284.63959490741</v>
+        <v>46284.66527777778</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
@@ -4170,7 +4214,7 @@
         <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="3" t="n">
@@ -4181,7 +4225,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4191,16 +4235,16 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T44" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U44" s="4" t="n">
         <v>0</v>
@@ -4210,73 +4254,61 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00056</t>
+          <t>DIM-2026-00065</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46284.63946759259</v>
+        <v>46284.664375</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.664375</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -4288,59 +4320,55 @@
         </is>
       </c>
       <c r="T45" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00055</t>
+          <t>DIM-2026-00064</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46284.63944444444</v>
+        <v>46284.66436342592</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -4350,113 +4378,113 @@
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.66436342592</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T46" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00054</t>
+          <t>DIM-2026-00063</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46284.63943287037</v>
+        <v>46284.66435185185</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T47" s="4" t="n">
-        <v>10260</v>
+        <v>62480</v>
       </c>
       <c r="U47" s="4" t="n">
         <v>0</v>
@@ -4466,11 +4494,11 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00053</t>
+          <t>DIM-2026-00062</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46284.59835648148</v>
+        <v>46284.66431712963</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
@@ -4484,15 +4512,19 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -4504,7 +4536,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>3</v>
@@ -4521,7 +4553,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -4540,7 +4572,7 @@
         </is>
       </c>
       <c r="T48" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U48" s="4" t="n">
         <v>0</v>
@@ -4550,85 +4582,81 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00052</t>
+          <t>DIM-2026-00061</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46284.59787037037</v>
+        <v>46284.66429398148</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="3" t="n">
-        <v>46296.375</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T49" s="4" t="n">
-        <v>61170</v>
+        <v>10260</v>
       </c>
       <c r="U49" s="4" t="n">
         <v>0</v>
@@ -4638,11 +4666,11 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00051</t>
+          <t>DIM-2026-00060</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46284.59783564815</v>
+        <v>46284.66428240741</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -4690,7 +4718,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O50" s="2" t="n">
         <v>8</v>
@@ -4722,11 +4750,11 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00050</t>
+          <t>DIM-2026-00059</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>46284.59783564815</v>
+        <v>46284.63960648148</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -4735,22 +4763,22 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4758,13 +4786,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -4774,43 +4798,43 @@
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46287.63960648148</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T51" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00049</t>
+          <t>DIM-2026-00057</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46284.5900925926</v>
+        <v>46284.63959490741</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -4824,19 +4848,15 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -4848,13 +4868,13 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="3" t="n">
@@ -4865,7 +4885,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -4875,16 +4895,16 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T52" s="4" t="n">
-        <v>61170</v>
+        <v>62480</v>
       </c>
       <c r="U52" s="4" t="n">
         <v>0</v>
@@ -4894,49 +4914,41 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00048</t>
+          <t>DIM-2026-00058</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>46284.59005787037</v>
+        <v>46284.63959490741</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -4946,113 +4958,117 @@
       </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.63959490741</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T53" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00047</t>
+          <t>DIM-2026-00056</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46284.59005787037</v>
+        <v>46284.63946759259</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T54" s="4" t="n">
-        <v>10260</v>
+        <v>61170</v>
       </c>
       <c r="U54" s="4" t="n">
         <v>0</v>
@@ -5062,11 +5078,11 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00046</t>
+          <t>DIM-2026-00055</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>46284.5899074074</v>
+        <v>46284.63944444444</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -5075,22 +5091,22 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -5098,9 +5114,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -5110,113 +5130,113 @@
       </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="3" t="n">
-        <v>46287.5899074074</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P55" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T55" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00044</t>
+          <t>DIM-2026-00054</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46284.58989583333</v>
+        <v>46284.63943287037</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T56" s="4" t="n">
-        <v>62480</v>
+        <v>10260</v>
       </c>
       <c r="U56" s="4" t="n">
         <v>0</v>
@@ -5226,11 +5246,11 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00045</t>
+          <t>DIM-2026-00053</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>46284.58989583333</v>
+        <v>46284.59835648148</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -5239,44 +5259,56 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="3" t="n">
-        <v>46285.58989583333</v>
+        <v>46296.375</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -5288,25 +5320,21 @@
         </is>
       </c>
       <c r="T57" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00043</t>
+          <t>DIM-2026-00052</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46284.58836805556</v>
+        <v>46284.59787037037</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
@@ -5320,15 +5348,19 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -5340,7 +5372,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>3</v>
@@ -5357,7 +5389,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -5376,7 +5408,7 @@
         </is>
       </c>
       <c r="T58" s="4" t="n">
-        <v>57870</v>
+        <v>61170</v>
       </c>
       <c r="U58" s="4" t="n">
         <v>0</v>
@@ -5386,11 +5418,11 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00042</t>
+          <t>DIM-2026-00050</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>46284.58796296296</v>
+        <v>46284.59783564815</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -5399,22 +5431,22 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -5422,9 +5454,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -5434,73 +5470,81 @@
       </c>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="3" t="n">
-        <v>46287.58796296296</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P59" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q59" s="2" t="inlineStr"/>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T59" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00041</t>
+          <t>DIM-2026-00051</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>46284.58795138889</v>
+        <v>46284.59783564815</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -5510,43 +5554,43 @@
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="3" t="n">
-        <v>46285.58795138889</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P60" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T60" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00040</t>
+          <t>DIM-2026-00049</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>46284.58793981482</v>
+        <v>46284.5900925926</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
@@ -5560,15 +5604,19 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -5580,13 +5628,13 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="3" t="n">
@@ -5597,7 +5645,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chisinau, str. Test 1</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -5607,16 +5655,16 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T61" s="4" t="n">
-        <v>62480</v>
+        <v>61170</v>
       </c>
       <c r="U61" s="4" t="n">
         <v>0</v>
@@ -5626,85 +5674,81 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00039</t>
+          <t>DIM-2026-00047</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46284.58790509259</v>
+        <v>46284.59005787037</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T62" s="4" t="n">
-        <v>61170</v>
+        <v>10260</v>
       </c>
       <c r="U62" s="4" t="n">
         <v>0</v>
@@ -5714,11 +5758,11 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00038</t>
+          <t>DIM-2026-00048</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>46284.58788194445</v>
+        <v>46284.59005787037</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
@@ -5798,11 +5842,11 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00037</t>
+          <t>DIM-2026-00046</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46284.58787037037</v>
+        <v>46284.5899074074</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
@@ -5811,22 +5855,22 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5834,13 +5878,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -5850,43 +5890,43 @@
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46287.5899074074</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
       <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T64" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00036</t>
+          <t>DIM-2026-00044</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>46284.58694444445</v>
+        <v>46284.58989583333</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
@@ -5926,7 +5966,7 @@
         <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="3" t="n">
@@ -5937,7 +5977,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -5947,16 +5987,16 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T65" s="4" t="n">
-        <v>57870</v>
+        <v>62480</v>
       </c>
       <c r="U65" s="4" t="n">
         <v>0</v>
@@ -5966,11 +6006,11 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00035</t>
+          <t>DIM-2026-00045</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>46284.58646990741</v>
+        <v>46284.58989583333</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
@@ -5979,60 +6019,44 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58989583333</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
       <c r="R66" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6044,91 +6068,95 @@
         </is>
       </c>
       <c r="T66" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00034</t>
+          <t>DIM-2026-00043</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>46284.58644675926</v>
+        <v>46284.58836805556</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T67" s="4" t="n">
-        <v>10260</v>
+        <v>57870</v>
       </c>
       <c r="U67" s="4" t="n">
         <v>0</v>
@@ -6138,11 +6166,11 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00033</t>
+          <t>DIM-2026-00042</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>46284.58643518519</v>
+        <v>46284.58796296296</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
@@ -6151,22 +6179,22 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -6174,13 +6202,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -6190,43 +6214,43 @@
       </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46287.58796296296</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
       <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T68" s="4" t="n">
-        <v>10260</v>
+        <v>0</v>
       </c>
       <c r="U68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00032</t>
+          <t>DIM-2026-00041</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>46284.58615740741</v>
+        <v>46284.58795138889</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
@@ -6235,60 +6259,44 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58795138889</v>
       </c>
       <c r="O69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr"/>
       <c r="R69" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6300,91 +6308,95 @@
         </is>
       </c>
       <c r="T69" s="4" t="n">
-        <v>61170</v>
+        <v>0</v>
       </c>
       <c r="U69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00031</t>
+          <t>DIM-2026-00040</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>46284.58614583333</v>
+        <v>46284.58793981482</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T70" s="4" t="n">
-        <v>0</v>
+        <v>62480</v>
       </c>
       <c r="U70" s="4" t="n">
         <v>0</v>
@@ -6394,81 +6406,85 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00030</t>
+          <t>DIM-2026-00039</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>46284.58613425926</v>
+        <v>46284.58790509259</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T71" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U71" s="4" t="n">
         <v>0</v>
@@ -6478,11 +6494,11 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00029</t>
+          <t>DIM-2026-00038</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>46284.585625</v>
+        <v>46284.58788194445</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
@@ -6491,22 +6507,22 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369000111</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Rezidential Grup SRL</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -6514,9 +6530,13 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -6526,73 +6546,81 @@
       </c>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="3" t="n">
-        <v>46287.585625</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P72" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T72" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00028</t>
+          <t>DIM-2026-00037</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>46284.58561342592</v>
+        <v>46284.58787037037</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -6602,43 +6630,43 @@
       </c>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="3" t="n">
-        <v>46285.58561342592</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P73" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T73" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00027</t>
+          <t>DIM-2026-00036</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>46284.58560185185</v>
+        <v>46284.58694444445</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -6678,7 +6706,7 @@
         <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="3" t="n">
@@ -6689,7 +6717,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
+          <t>Chișinău, str. Ion Creangă 45</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -6699,16 +6727,16 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T74" s="4" t="n">
-        <v>62480</v>
+        <v>57870</v>
       </c>
       <c r="U74" s="4" t="n">
         <v>0</v>
@@ -6718,61 +6746,73 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00026</t>
+          <t>DIM-2026-00035</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>46284.58523148148</v>
+        <v>46284.58646990741</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="3" t="n">
-        <v>46287.58523148148</v>
+        <v>46296.375</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
-      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -6784,55 +6824,59 @@
         </is>
       </c>
       <c r="T75" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U75" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00025</t>
+          <t>DIM-2026-00034</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>46284.58521990741</v>
+        <v>46284.58644675926</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -6842,113 +6886,113 @@
       </c>
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="3" t="n">
-        <v>46285.58521990741</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P76" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T76" s="4" t="n">
-        <v>0</v>
+        <v>10260</v>
       </c>
       <c r="U76" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00024</t>
+          <t>DIM-2026-00033</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>46284.58521990741</v>
+        <v>46284.58643518519</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T77" s="4" t="n">
-        <v>62480</v>
+        <v>10260</v>
       </c>
       <c r="U77" s="4" t="n">
         <v>0</v>
@@ -6958,61 +7002,73 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00023</t>
+          <t>DIM-2026-00032</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>46284.58506944445</v>
+        <v>46284.58615740741</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>partner_apply</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Прораб Тестов</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>+37369998877</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>ТестСтрой SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="3" t="n">
-        <v>46287.58506944445</v>
+        <v>46296.375</v>
       </c>
       <c r="O78" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -7024,55 +7080,59 @@
         </is>
       </c>
       <c r="T78" s="4" t="n">
-        <v>0</v>
+        <v>61170</v>
       </c>
       <c r="U78" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="2" t="inlineStr">
-        <is>
-          <t>Заявка на подключение партнёра</t>
-        </is>
-      </c>
+      <c r="V78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00022</t>
+          <t>DIM-2026-00031</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>46284.58505787037</v>
+        <v>46284.58614583333</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>contact_form</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Тест Контакт</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>+37360112233</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -7082,21 +7142,25 @@
       </c>
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="3" t="n">
-        <v>46285.58505787037</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P79" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
       <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T79" s="4" t="n">
@@ -7105,90 +7169,86 @@
       <c r="U79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="2" t="inlineStr">
-        <is>
-          <t>Свободная заявка с формы контактов</t>
-        </is>
-      </c>
+      <c r="V79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00021</t>
+          <t>DIM-2026-00030</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46284.5850462963</v>
+        <v>46284.58613425926</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Бытовка 6 м</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>46296.375</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T80" s="4" t="n">
-        <v>62480</v>
+        <v>0</v>
       </c>
       <c r="U80" s="4" t="n">
         <v>0</v>
@@ -7198,11 +7258,11 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00020</t>
+          <t>DIM-2026-00029</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>46284.58466435185</v>
+        <v>46284.585625</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -7246,7 +7306,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="3" t="n">
-        <v>46287.58466435185</v>
+        <v>46287.585625</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>4</v>
@@ -7278,11 +7338,11 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00019</t>
+          <t>DIM-2026-00028</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46284.58466435185</v>
+        <v>46284.58561342592</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7382,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>46285.58466435185</v>
+        <v>46285.58561342592</v>
       </c>
       <c r="O82" s="2" t="n">
         <v>4</v>
@@ -7354,11 +7414,11 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00018</t>
+          <t>DIM-2026-00027</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>46284.58465277778</v>
+        <v>46284.58560185185</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
@@ -7438,73 +7498,61 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00017</t>
+          <t>DIM-2026-00026</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46284.57537037037</v>
+        <v>46284.58523148148</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Constructor Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.58523148148</v>
       </c>
       <c r="O84" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>Chisinau, str. Test 1</t>
-        </is>
-      </c>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
       <c r="R84" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -7516,91 +7564,95 @@
         </is>
       </c>
       <c r="T84" s="4" t="n">
-        <v>17930</v>
+        <v>0</v>
       </c>
       <c r="U84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00016</t>
+          <t>DIM-2026-00024</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>46284.57534722222</v>
+        <v>46284.58521990741</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46296.375</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q85" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T85" s="4" t="n">
-        <v>23600</v>
+        <v>62480</v>
       </c>
       <c r="U85" s="4" t="n">
         <v>0</v>
@@ -7610,49 +7662,41 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00015</t>
+          <t>DIM-2026-00025</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>46284.57534722222</v>
+        <v>46284.58521990741</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -7662,101 +7706,93 @@
       </c>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46285.58521990741</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P86" s="2" t="inlineStr"/>
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T86" s="4" t="n">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="U86" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00014</t>
+          <t>DIM-2026-00023</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>46284.57185185186</v>
+        <v>46284.58506944445</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
+          <t>+37369998877</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>ТестСтрой SRL</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>46296.375</v>
+        <v>46287.58506944445</v>
       </c>
       <c r="O87" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -7768,21 +7804,25 @@
         </is>
       </c>
       <c r="T87" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00013</t>
+          <t>DIM-2026-00022</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46284.57065972222</v>
+        <v>46284.58505787037</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
@@ -7791,56 +7831,44 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Ион Мунтяну</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>+37369456789</t>
+          <t>+37360112233</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>place</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>Бытовка 6 м</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>46296.375</v>
+        <v>46285.58505787037</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, str. Ion Creangă 45</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -7852,21 +7880,25 @@
         </is>
       </c>
       <c r="T88" s="4" t="n">
-        <v>57870</v>
+        <v>0</v>
       </c>
       <c r="U88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00012</t>
+          <t>DIM-2026-00021</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>46284.56907407408</v>
+        <v>46284.5850462963</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
@@ -7880,19 +7912,15 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Тест Клиент</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>+37369123456</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Constructor Grup SRL</t>
-        </is>
-      </c>
+          <t>+37369456789</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>place</t>
@@ -7904,13 +7932,13 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="3" t="n">
@@ -7921,7 +7949,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>Chisinau, str. Test 1</t>
+          <t>Chișinău, str. Test 1</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -7931,16 +7959,16 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="T89" s="4" t="n">
-        <v>17930</v>
+        <v>62480</v>
       </c>
       <c r="U89" s="4" t="n">
         <v>0</v>
@@ -7950,49 +7978,41 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00011</t>
+          <t>DIM-2026-00019</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>46284.5690625</v>
+        <v>46284.58466435185</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>contact_form</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Контакт</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Rezidential Grup SRL</t>
-        </is>
-      </c>
+          <t>+37360112233</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -8002,43 +8022,43 @@
       </c>
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46285.58466435185</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P90" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P90" s="2" t="inlineStr"/>
       <c r="Q90" s="2" t="inlineStr"/>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T90" s="4" t="n">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="U90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>Свободная заявка с формы контактов</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00010</t>
+          <t>DIM-2026-00020</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>46284.56905092593</v>
+        <v>46284.58466435185</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
@@ -8047,22 +8067,22 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>partner_apply</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Прораб Тестов</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369998877</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>ТестСтрой SRL</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -8070,13 +8090,9 @@
           <t>construction</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>smoke</t>
-        </is>
-      </c>
+      <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -8086,43 +8102,43 @@
       </c>
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46287.58466435185</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P91" s="2" t="inlineStr">
-        <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
       <c r="Q91" s="2" t="inlineStr"/>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T91" s="4" t="n">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="U91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>Заявка на подключение партнёра</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00001</t>
+          <t>DIM-2026-00018</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.58465277778</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
@@ -8136,12 +8152,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Ион Русу</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>+37369111222</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -8156,30 +8172,34 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="3" t="n">
-        <v>46286.94390046296</v>
+        <v>46296.375</v>
       </c>
       <c r="O92" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, с. Стэучень</t>
-        </is>
-      </c>
-      <c r="Q92" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>quoted</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
@@ -8188,7 +8208,7 @@
         </is>
       </c>
       <c r="T92" s="4" t="n">
-        <v>9900</v>
+        <v>62480</v>
       </c>
       <c r="U92" s="4" t="n">
         <v>0</v>
@@ -8198,95 +8218,99 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00009</t>
+          <t>DIM-2026-00017</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57537037037</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>B2C</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>portal</t>
+          <t>wizard</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Дмитрий Попа</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>+37369000111</t>
+          <t>+37369123456</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Rezidential Grup SRL</t>
+          <t>Constructor Grup SRL</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>construction</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>46291.3334837963</v>
+        <v>46296.375</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Богдан Воевод 12</t>
-        </is>
-      </c>
-      <c r="Q93" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>contacted</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>under_review</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T93" s="4" t="n">
-        <v>0</v>
+        <v>17930</v>
       </c>
       <c r="U93" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00008</t>
+          <t>DIM-2026-00015</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57534722222</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
@@ -8320,11 +8344,11 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -8334,7 +8358,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>46284.3334837963</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O94" s="2" t="n">
         <v>8</v>
@@ -8347,30 +8371,30 @@
       <c r="Q94" s="2" t="inlineStr"/>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T94" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U94" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00007</t>
+          <t>DIM-2026-00016</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57534722222</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
@@ -8404,11 +8428,11 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Бетонирование перекрытия</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -8418,7 +8442,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>46277.3334837963</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O95" s="2" t="n">
         <v>8</v>
@@ -8431,30 +8455,30 @@
       <c r="Q95" s="2" t="inlineStr"/>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T95" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U95" s="4" t="n">
-        <v>16720</v>
+        <v>0</v>
       </c>
       <c r="V95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00006</t>
+          <t>DIM-2026-00014</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57185185186</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
@@ -8468,47 +8492,51 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Анна Ковальчук</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>+37379333444</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>lift_height</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Трансформатор</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>46293.86056712963</v>
+        <v>46296.375</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, промзона</t>
-        </is>
-      </c>
-      <c r="Q96" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
           <t>new</t>
@@ -8520,25 +8548,21 @@
         </is>
       </c>
       <c r="T96" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="5" t="inlineStr">
-        <is>
-          <t>Масса груза превышает 60 % возможностей парка — требуется инженерный расчёт; Работа вблизи ЛЭП</t>
-        </is>
-      </c>
+      <c r="V96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00005</t>
+          <t>DIM-2026-00013</t>
         </is>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.57065972222</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
@@ -8552,12 +8576,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Ион Русу</t>
+          <t>Ион Мунтяну</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>+37369111222</t>
+          <t>+37369456789</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
@@ -8568,57 +8592,61 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Септик</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="3" t="n">
-        <v>46264.56890046296</v>
+        <v>46296.375</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, с. Стэучень</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="inlineStr"/>
+          <t>Chișinău, str. Ion Creangă 45</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T97" s="4" t="n">
-        <v>0</v>
+        <v>57870</v>
       </c>
       <c r="U97" s="4" t="n">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="V97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00004</t>
+          <t>DIM-2026-00012</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.56907407408</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
@@ -8632,204 +8660,220 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Виктор Чеботарь</t>
+          <t>Тест Клиент</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>+37360777888</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
+          <t>+37369123456</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Constructor Grup SRL</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>unload</t>
+          <t>place</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Плиты перекрытия</t>
+          <t>Бытовка 6 м</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="3" t="n">
-        <v>46285.6522337963</v>
+        <v>46296.375</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Мунчешть 271</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="inlineStr"/>
+          <t>Chisinau, str. Test 1</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>won</t>
+          <t>new</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="T98" s="4" t="n">
-        <v>0</v>
+        <v>17930</v>
       </c>
       <c r="U98" s="4" t="n">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="V98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00003</t>
+          <t>DIM-2026-00011</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.5690625</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Сергей Мунтян</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>+37368555666</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>lift_height</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Металлоферма</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="3" t="n">
-        <v>46290.94390046296</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, ул. Узинелор 5</t>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>contacted</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>under_review</t>
         </is>
       </c>
       <c r="T99" s="4" t="n">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="U99" s="4" t="n">
-        <v>17600</v>
+        <v>0</v>
       </c>
       <c r="V99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>DIM-2026-00002</t>
+          <t>DIM-2026-00010</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46284.56890046296</v>
+        <v>46284.56905092593</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>B2C</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>wizard</t>
+          <t>portal</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Анна Ковальчук</t>
+          <t>Дмитрий Попа</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>+37379333444</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>install</t>
+          <t>construction</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Кондиционер / чиллер</t>
+          <t>smoke</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="3" t="n">
-        <v>46288.9022337963</v>
+        <v>46301.33333333334</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>Chișinău, бул. Дачия 47</t>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -8844,70 +8888,806 @@
         </is>
       </c>
       <c r="T100" s="4" t="n">
+        <v>23600</v>
+      </c>
+      <c r="U100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00001</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Ион Русу</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>+37369111222</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Бытовка 6 м</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="3" t="n">
+        <v>46286.94390046296</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, с. Стэучень</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="T101" s="4" t="n">
+        <v>9900</v>
+      </c>
+      <c r="U101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00002</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Анна Ковальчук</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>+37379333444</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>install</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Кондиционер / чиллер</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="3" t="n">
+        <v>46288.9022337963</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, бул. Дачия 47</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>under_review</t>
+        </is>
+      </c>
+      <c r="T102" s="4" t="n">
         <v>11200</v>
       </c>
-      <c r="U100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n"/>
-      <c r="B101" s="2" t="n"/>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="n"/>
-      <c r="J101" s="2" t="n"/>
-      <c r="K101" s="2" t="n"/>
-      <c r="L101" s="2" t="n"/>
-      <c r="M101" s="2" t="n"/>
-      <c r="N101" s="2" t="n"/>
-      <c r="O101" s="2" t="n"/>
-      <c r="P101" s="2" t="n"/>
-      <c r="Q101" s="2" t="n"/>
-      <c r="R101" s="2" t="n"/>
-      <c r="S101" s="2" t="n"/>
-      <c r="T101" s="2" t="n"/>
-      <c r="U101" s="2" t="n"/>
-      <c r="V101" s="2" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
+      <c r="U102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00003</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Сергей Мунтян</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>+37368555666</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>lift_height</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Металлоферма</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="3" t="n">
+        <v>46290.94390046296</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Узинелор 5</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>quoted</t>
+        </is>
+      </c>
+      <c r="T103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="4" t="n">
+        <v>17600</v>
+      </c>
+      <c r="V103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00004</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Виктор Чеботарь</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>+37360777888</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>unload</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Плиты перекрытия</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="3" t="n">
+        <v>46285.6522337963</v>
+      </c>
+      <c r="O104" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Мунчешть 271</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="T104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="4" t="n">
+        <v>6800</v>
+      </c>
+      <c r="V104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00005</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Ион Русу</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>+37369111222</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Септик</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="3" t="n">
+        <v>46264.56890046296</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, с. Стэучень</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="T105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="V105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00006</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>B2C</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>wizard</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Анна Ковальчук</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>+37379333444</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>lift_height</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Трансформатор</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="3" t="n">
+        <v>46293.86056712963</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, промзона</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="T106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="5" t="inlineStr">
+        <is>
+          <t>Масса груза превышает 60 % возможностей парка — требуется инженерный расчёт; Работа вблизи ЛЭП</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00007</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий Попа</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Бетонирование перекрытия</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="3" t="n">
+        <v>46277.3334837963</v>
+      </c>
+      <c r="O107" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="T107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="4" t="n">
+        <v>16720</v>
+      </c>
+      <c r="V107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00008</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий Попа</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Бетонирование перекрытия</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="3" t="n">
+        <v>46284.3334837963</v>
+      </c>
+      <c r="O108" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>won</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="T108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="4" t="n">
+        <v>16720</v>
+      </c>
+      <c r="V108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>DIM-2026-00009</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>46284.56890046296</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Дмитрий Попа</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>+37369000111</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Rezidential Grup SRL</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Бетонирование перекрытия</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="3" t="n">
+        <v>46291.3334837963</v>
+      </c>
+      <c r="O109" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>Chișinău, ул. Богдан Воевод 12</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>under_review</t>
+        </is>
+      </c>
+      <c r="T109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="4" t="n">
+        <v>16720</v>
+      </c>
+      <c r="V109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
+      <c r="Q110" s="2" t="n"/>
+      <c r="R110" s="2" t="n"/>
+      <c r="S110" s="2" t="n"/>
+      <c r="T110" s="2" t="n"/>
+      <c r="U110" s="2" t="n"/>
+      <c r="V110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr"/>
-      <c r="C102" s="6" t="inlineStr"/>
-      <c r="D102" s="6" t="inlineStr"/>
-      <c r="E102" s="6" t="inlineStr"/>
-      <c r="F102" s="6" t="inlineStr"/>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr"/>
-      <c r="I102" s="6" t="inlineStr"/>
-      <c r="J102" s="6" t="inlineStr"/>
-      <c r="K102" s="6" t="inlineStr"/>
-      <c r="L102" s="6" t="inlineStr"/>
-      <c r="M102" s="6" t="inlineStr"/>
-      <c r="N102" s="6" t="inlineStr"/>
-      <c r="O102" s="6" t="inlineStr"/>
-      <c r="P102" s="6" t="inlineStr"/>
-      <c r="Q102" s="6" t="inlineStr"/>
-      <c r="R102" s="6" t="inlineStr"/>
-      <c r="S102" s="6" t="inlineStr"/>
-      <c r="T102" s="6">
-        <f>SUM(T2:T98)</f>
+      <c r="B111" s="6" t="inlineStr"/>
+      <c r="C111" s="6" t="inlineStr"/>
+      <c r="D111" s="6" t="inlineStr"/>
+      <c r="E111" s="6" t="inlineStr"/>
+      <c r="F111" s="6" t="inlineStr"/>
+      <c r="G111" s="6" t="inlineStr"/>
+      <c r="H111" s="6" t="inlineStr"/>
+      <c r="I111" s="6" t="inlineStr"/>
+      <c r="J111" s="6" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr"/>
+      <c r="L111" s="6" t="inlineStr"/>
+      <c r="M111" s="6" t="inlineStr"/>
+      <c r="N111" s="6" t="inlineStr"/>
+      <c r="O111" s="6" t="inlineStr"/>
+      <c r="P111" s="6" t="inlineStr"/>
+      <c r="Q111" s="6" t="inlineStr"/>
+      <c r="R111" s="6" t="inlineStr"/>
+      <c r="S111" s="6" t="inlineStr"/>
+      <c r="T111" s="6">
+        <f>SUM(T2:T107)</f>
         <v/>
       </c>
-      <c r="U102" s="6">
-        <f>SUM(U2:U98)</f>
+      <c r="U111" s="6">
+        <f>SUM(U2:U107)</f>
         <v/>
       </c>
-      <c r="V102" s="6" t="inlineStr"/>
+      <c r="V111" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>
